--- a/output/pdf_financials_xlsx/WGM.xlsx
+++ b/output/pdf_financials_xlsx/WGM.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.122961</v>
+        <v>0.201394</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.884829</v>
+        <v>3.557733</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.122961</v>
+        <v>-0.201394</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.884829</v>
+        <v>-3.557733</v>
       </c>
     </row>
     <row r="12">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.317743</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.202164</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.317743</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.202164</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.331988</v>
+        <v>0.014245</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.221869</v>
+        <v>0.019705</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">

--- a/output/pdf_financials_xlsx/WGM.xlsx
+++ b/output/pdf_financials_xlsx/WGM.xlsx
@@ -2946,7 +2946,11 @@
           <t>Proceeds from shares issued for cash</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.37</v>
       </c>
